--- a/tools/excel/nist/nist-csf-2.0.xlsx
+++ b/tools/excel/nist/nist-csf-2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\nist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D726EF-2A5B-4533-923D-F99E21E1C528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7824B28F-81C9-43D2-9BAD-410A8DCC4361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19210" yWindow="-21710" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24192" yWindow="-11808" windowWidth="25668" windowHeight="17304" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,15 @@
     <sheet name="csf_content" sheetId="3" r:id="rId3"/>
     <sheet name="scores_meta" sheetId="4" r:id="rId4"/>
     <sheet name="scores_content" sheetId="5" r:id="rId5"/>
+    <sheet name="urn_pref_meta" sheetId="6" r:id="rId6"/>
+    <sheet name="urn_pref_content" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="1107">
   <si>
     <t>type</t>
   </si>
@@ -41,90 +43,90 @@
     <t>version</t>
   </si>
   <si>
+    <t>locale</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>ref_id</t>
+  </si>
+  <si>
+    <t>NIST-CSF-2.0</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>NIST CSF version 2.0</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>National Institute of Standards and Technology - Cybersecurity Framework (CSF 2.0)</t>
+  </si>
+  <si>
+    <t>copyright</t>
+  </si>
+  <si>
+    <t>With the exception of material marked as copyrighted, information presented on NIST sites are considered public information and may be distributed or copied.</t>
+  </si>
+  <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
+    <t>packager</t>
+  </si>
+  <si>
+    <t>intuitem</t>
+  </si>
+  <si>
+    <t>name[fr]</t>
+  </si>
+  <si>
+    <t>description[fr]</t>
+  </si>
+  <si>
+    <t>name[es]</t>
+  </si>
+  <si>
+    <t>description[es]</t>
+  </si>
+  <si>
+    <t>framework</t>
+  </si>
+  <si>
+    <t>base_urn</t>
+  </si>
+  <si>
+    <t>urn:intuitem:risk:req_node:nist-csf-2.0</t>
+  </si>
+  <si>
+    <t>urn:intuitem:risk:framework:nist-csf-2.0</t>
+  </si>
+  <si>
+    <t>NIST CSF v2.0</t>
+  </si>
+  <si>
+    <t>NIST Cybersecurity Framework</t>
+  </si>
+  <si>
+    <t>min_score</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>max_score</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>locale</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>ref_id</t>
-  </si>
-  <si>
-    <t>NIST-CSF-2.0</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>NIST CSF version 2.0</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>National Institute of Standards and Technology - Cybersecurity Framework (CSF 2.0)</t>
-  </si>
-  <si>
-    <t>copyright</t>
-  </si>
-  <si>
-    <t>With the exception of material marked as copyrighted, information presented on NIST sites are considered public information and may be distributed or copied.</t>
-  </si>
-  <si>
-    <t>provider</t>
-  </si>
-  <si>
-    <t>NIST</t>
-  </si>
-  <si>
-    <t>packager</t>
-  </si>
-  <si>
-    <t>intuitem</t>
-  </si>
-  <si>
-    <t>name[fr]</t>
-  </si>
-  <si>
-    <t>description[fr]</t>
-  </si>
-  <si>
-    <t>name[es]</t>
-  </si>
-  <si>
-    <t>description[es]</t>
-  </si>
-  <si>
-    <t>framework</t>
-  </si>
-  <si>
-    <t>base_urn</t>
-  </si>
-  <si>
-    <t>urn:intuitem:risk:req_node:nist-csf-2.0</t>
-  </si>
-  <si>
-    <t>urn:intuitem:risk:framework:nist-csf-2.0</t>
-  </si>
-  <si>
-    <t>NIST CSF v2.0</t>
-  </si>
-  <si>
-    <t>NIST Cybersecurity Framework</t>
-  </si>
-  <si>
-    <t>min_score</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>max_score</t>
-  </si>
-  <si>
     <t>scores_definition</t>
   </si>
   <si>
@@ -144,6 +146,9 @@
   </si>
   <si>
     <t>annotation[es]</t>
+  </si>
+  <si>
+    <t>reference_controls</t>
   </si>
   <si>
     <t>GV</t>
@@ -213,6 +218,9 @@
   <si>
     <t>1º: Riesgo de 1ª parte
 Ex1: Compartir la misión de la organización (por ejemplo, a través de declaraciones de visión y misión, marketing y estrategias de servicio) para proporcionar una base para identificar los riesgos que pueden obstaculizar esa misión</t>
+  </si>
+  <si>
+    <t>1:DOC.CONTEXT, 1:DOC.OVERVIEW, 1:POL.MAIN</t>
   </si>
   <si>
     <t>GV.OC-02</t>
@@ -243,6 +251,9 @@
 3º: Riesgo de 3ª parte
 Ex1: Identificar a las partes interesadas internas relevantes y sus expectativas relacionadas con la ciberseguridad (por ejemplo, expectativas de rendimiento y riesgo de funcionarios, directores y asesores; expectativas culturales de los empleados)
 Ex2: Identificar a las partes interesadas externas relevantes y sus expectativas relacionadas con la ciberseguridad (por ejemplo, expectativas de privacidad de los clientes, expectativas comerciales de las asociaciones, expectativas de cumplimiento de los reguladores, expectativas éticas de la sociedad)</t>
+  </si>
+  <si>
+    <t>1:DOC.CONTEXT, 1:DOC.COM</t>
   </si>
   <si>
     <t>GV.OC-03</t>
@@ -278,6 +289,9 @@
 Ex3: Alinear la estrategia de ciberseguridad de la organización con los requisitos legales, regulatorios y contractuales</t>
   </si>
   <si>
+    <t>1:DOC.LEGAL, 1:POL.MAIN</t>
+  </si>
+  <si>
     <t>GV.OC-04</t>
   </si>
   <si>
@@ -311,6 +325,9 @@
 Ex3: Establecer y comunicar objetivos de resiliencia (p. ej., objetivos de tiempo de recuperación) para la entrega de capacidades y servicios críticos en varios estados operativos (p. ej., bajo ataque, durante la recuperación, operación normal)</t>
   </si>
   <si>
+    <t>1:DOC.CONTEXT, 1:DOC.SCOPE, 1:DOC.BIA</t>
+  </si>
+  <si>
     <t>GV.OC-05</t>
   </si>
   <si>
@@ -336,6 +353,9 @@
     <t>Ex1: Crear un inventario de las dependencias de la organización de recursos externos (por ejemplo, instalaciones, proveedores de alojamiento basado en la nube) y sus relaciones con los activos de la organización y las funciones comerciales
 Ex2: Identificar y documentar las dependencias externas que son puntos potenciales de falla para las capacidades y servicios críticos de la organización, y compartir esa información con el personal adecuado
 3º: Riesgo de 3ª parte</t>
+  </si>
+  <si>
+    <t>1:DOC.CONTEXT, 1:DOC.BIA, 1:DOC.SUPPLIER_REGISTER</t>
   </si>
   <si>
     <t>GV.RM</t>
@@ -387,6 +407,9 @@
 Ex1: Actualizar los objetivos de gestión de riesgos de ciberseguridad a corto y largo plazo como parte de la planificación estratégica anual y cuando se produzcan cambios importantes
 Ex2: Establecer objetivos medibles para la gestión de riesgos de ciberseguridad (por ejemplo, gestionar la calidad de la formación de los usuarios, garantizar una protección adecuada contra los riesgos de los sistemas de control industrial)
 Ex3: Los líderes sénior acuerdan los objetivos de ciberseguridad y los utilizan para medir y gestionar el riesgo y el rendimiento</t>
+  </si>
+  <si>
+    <t>1:POL.RISK, 1:DOC.SO_REGISTER</t>
   </si>
   <si>
     <t>GV.RM-02</t>
@@ -422,6 +445,9 @@
 Ex3: Refinar periódicamente los objetivos de la organización y el apetito de riesgo en función de la exposición al riesgo conocida y el riesgo residual</t>
   </si>
   <si>
+    <t>1:DOC.RISK_APPETITE, 1:POL.RISK</t>
+  </si>
+  <si>
     <t>GV.RM-03</t>
   </si>
   <si>
@@ -452,6 +478,9 @@
 Ex3: Establecer criterios para escalar los riesgos de ciberseguridad dentro de la gestión de riesgos empresariales</t>
   </si>
   <si>
+    <t>1:POL.RISK, 1:DOC.RISK_REGISTER</t>
+  </si>
+  <si>
     <t>GV.RM-04</t>
   </si>
   <si>
@@ -482,6 +511,9 @@
 Ex3: Documentar las condiciones en las que los modelos de responsabilidad compartida son aceptables (por ejemplo, externalización de ciertas funciones de ciberseguridad, hacer que un tercero realice transacciones financieras en nombre de la organización, utilizar servicios basados en la nube pública)</t>
   </si>
   <si>
+    <t>1:POL.RISK, 1:DOC.RISK_APPETITE</t>
+  </si>
+  <si>
     <t>GV.RM-05</t>
   </si>
   <si>
@@ -510,6 +542,9 @@
 3º: Riesgo de 3ª parte
 Ex1: Determinar cómo actualizar a los altos ejecutivos, directores y gerentes sobre la postura de ciberseguridad de la organización a intervalos acordados
 Ex2: Identificar cómo se comunicarán entre sí todos los departamentos de la organización, como la dirección, las operaciones, los auditores internos, el departamento jurídico, el de adquisiciones, el de seguridad física y el de RRHH sobre los riesgos de ciberseguridad.</t>
+  </si>
+  <si>
+    <t>1:DOC.COM, 1:POL.RISK, 1:POL.SUPPLIER</t>
   </si>
   <si>
     <t>GV.RM-06</t>
@@ -627,6 +662,9 @@
 Ex2: Compartir las expectativas de los líderes con respecto a una cultura segura y ética, especialmente cuando los acontecimientos actuales presentan la oportunidad de destacar ejemplos positivos o negativos de gestión de riesgos de ciberseguridad.
 Ex3: Los líderes ordenan al CISO que mantenga una estrategia integral de riesgo de ciberseguridad y la revise y actualice al menos una vez al año y después de eventos importantes
 Ex4: Llevar a cabo revisiones para garantizar la autoridad y la coordinación adecuadas entre los responsables de la gestión del riesgo de ciberseguridad.</t>
+  </si>
+  <si>
+    <t>1:POL.MAIN, 1:DOC.RACI, 1:POL.EDUC</t>
   </si>
   <si>
     <t>GV.RR-02</t>
@@ -665,6 +703,9 @@
 Ex5: Articular claramente las responsabilidades de ciberseguridad dentro de las operaciones, las funciones de riesgo y las funciones de auditoría interna</t>
   </si>
   <si>
+    <t>1:DOC.RACI, 1:DOC.CONTROLS</t>
+  </si>
+  <si>
     <t>GV.RR-03</t>
   </si>
   <si>
@@ -698,6 +739,9 @@
 Ex3: Proporcionar las personas, los procesos y los recursos técnicos adecuados y suficientes para respaldar la estrategia de ciberseguridad.</t>
   </si>
   <si>
+    <t>1:POL.MAIN, 1:DOC.RACI</t>
+  </si>
+  <si>
     <t>GV.RR-04</t>
   </si>
   <si>
@@ -729,6 +773,9 @@
 Ex2: Considerar el conocimiento de ciberseguridad como un factor positivo en las decisiones de contratación, capacitación y retención
 Ex3: Realizar verificaciones de antecedentes antes de incorporar nuevo personal para roles confidenciales y repetir periódicamente las verificaciones de antecedentes para el personal con dichas funciones
 Ex4: Definir y hacer cumplir las obligaciones para que el personal conozca, se adhiera y defienda las políticas de seguridad en relación con sus funciones</t>
+  </si>
+  <si>
+    <t>1:PROC.HR_SECURITY, 1:PROC.BG_SCREENING, 1:PROC.DISCIPLINARY, 1:POL.EDUC</t>
   </si>
   <si>
     <t>GV.PO</t>
@@ -788,6 +835,9 @@
 Ex5: Exigir que el personal acuse recibo de la póliza cuando se contrata por primera vez, anualmente y siempre que se actualice la póliza.</t>
   </si>
   <si>
+    <t>1:POL.MAIN, 1:DOC.DOC_REGISTER</t>
+  </si>
+  <si>
     <t>GV.PO-02</t>
   </si>
   <si>
@@ -821,6 +871,9 @@
 Ej.4: Actualizar la política para reflejar los cambios en la tecnología (por ejemplo, la adopción de la inteligencia artificial) y los cambios en el negocio (por ejemplo, la adquisición de un nuevo negocio, los nuevos requisitos del contrato)</t>
   </si>
   <si>
+    <t>1:POL.MAIN, 1:DOC.DOC_REGISTER, 1:POL.AUDIT</t>
+  </si>
+  <si>
     <t>GV.OV</t>
   </si>
   <si>
@@ -867,6 +920,9 @@
     <t>1º: Riesgo de 1ª parte
 Ej. Medir qué tan bien la estrategia de gestión de riesgos y los resultados de riesgos han ayudado a los líderes a tomar decisiones y alcanzar los objetivos organizacionales.
 Ex2: Examinar si se deben ajustar las estrategias de riesgo de ciberseguridad que obstaculizan las operaciones o la innovación</t>
+  </si>
+  <si>
+    <t>1:DOC.MGMT_REVIEW, 1:POL.RISK</t>
   </si>
   <si>
     <t>GV.OV-02</t>
@@ -899,6 +955,9 @@
 Ex3: Revisar la estrategia a la luz de los incidentes de ciberseguridad</t>
   </si>
   <si>
+    <t>1:DOC.MGMT_REVIEW, 1:POL.RISK, 1:POL.AUDIT</t>
+  </si>
+  <si>
     <t>GV.OV-03</t>
   </si>
   <si>
@@ -927,6 +986,9 @@
 Ex1: Revisar los indicadores clave de rendimiento (KPI) para garantizar que las políticas y procedimientos de toda la organización alcancen los objetivos
 Ex2: Revisar los indicadores clave de riesgo (KRI) para identificar los riesgos a los que se enfrenta la organización, incluida la probabilidad y el impacto potencial
 Ex3: Recopilar y comunicar métricas sobre la gestión de riesgos de ciberseguridad con la alta dirección</t>
+  </si>
+  <si>
+    <t>1:DOC.MGMT_REVIEW, 1:DOC.NC_LOG, 1:POL.AUDIT</t>
   </si>
   <si>
     <t>GV.SC</t>
@@ -982,6 +1044,9 @@
 Ex3: Desarrollar e implementar procesos del programa basados en la estrategia, los objetivos, las políticas y los procedimientos acordados y realizados por las partes interesadas de la organización
 Ex4: Establecer un mecanismo interorganizacional que garantice la alineación entre las funciones que contribuyen a la gestión de riesgos de la cadena de suministro de ciberseguridad, como la ciberseguridad, la informática, las operaciones, el ámbito jurídico, el de recursos humanos y el de ingeniería
 3º: Riesgo de 3ª parte</t>
+  </si>
+  <si>
+    <t>1:POL.SUPPLIER</t>
   </si>
   <si>
     <t>GV.SC-02</t>
@@ -1029,6 +1094,9 @@
 3º: Riesgo de 3ª parte</t>
   </si>
   <si>
+    <t>1:POL.SUPPLIER, 1:DOC.RACI</t>
+  </si>
+  <si>
     <t>GV.SC-03</t>
   </si>
   <si>
@@ -1062,6 +1130,9 @@
 3º: Riesgo de 3ª parte</t>
   </si>
   <si>
+    <t>1:POL.SUPPLIER, 1:POL.RISK</t>
+  </si>
+  <si>
     <t>GV.SC-04</t>
   </si>
   <si>
@@ -1087,6 +1158,9 @@
     <t>Ex1: Desarrollar criterios para la criticidad de los proveedores basados, por ejemplo, en la sensibilidad de los datos procesados o en posesión de los proveedores, el grado de acceso a los sistemas de la organización y la importancia de los productos o servicios para la misión de la organización.
 Ex2: Mantener un registro de todos los proveedores y priorizar a los proveedores en función de los criterios de criticidad
 3º: Riesgo de 3ª parte</t>
+  </si>
+  <si>
+    <t>1:DOC.SUPPLIER_REGISTER, 1:POL.SUPPLIER</t>
   </si>
   <si>
     <t>GV.SC-05</t>
@@ -1140,6 +1214,9 @@
 3º: Riesgo de 3ª parte</t>
   </si>
   <si>
+    <t>1:POL.SUPPLIER, 1:PROC.TPRM_ASSESSMENT</t>
+  </si>
+  <si>
     <t>GV.SC-06</t>
   </si>
   <si>
@@ -1171,6 +1248,9 @@
 Ex3: Realizar evaluaciones de riesgos de los proveedores en relación con los requisitos empresariales y de ciberseguridad aplicables
 Ex4: Evaluar la autenticidad, integridad y seguridad de los productos críticos antes de su adquisición y uso
 3º: Riesgo de 3ª parte</t>
+  </si>
+  <si>
+    <t>1:PROC.TPRM_ASSESSMENT, 1:POL.SUPPLIER</t>
   </si>
   <si>
     <t>GV.SC-07</t>
@@ -1209,6 +1289,9 @@
 3º: Riesgo de 3ª parte</t>
   </si>
   <si>
+    <t>1:PROC.TPRM_ASSESSMENT, 1:DOC.SUPPLIER_REGISTER, 1:POL.SUPPLIER</t>
+  </si>
+  <si>
     <t>GV.SC-08</t>
   </si>
   <si>
@@ -1243,6 +1326,9 @@
 Ex4: Definir y coordinar los métodos y protocolos de comunicación de crisis entre la organización y sus proveedores críticos
 Ex5: Llevar a cabo sesiones colaborativas de lecciones aprendidas con proveedores críticos
 3º: Riesgo de 3ª parte</t>
+  </si>
+  <si>
+    <t>1:POL.SUPPLIER, 1:POL.INCIDENT, 1:PROC.INCIDENT</t>
   </si>
   <si>
     <t>GV.SC-09</t>
@@ -1323,6 +1409,9 @@
 3º: Riesgo de 3ª parte</t>
   </si>
   <si>
+    <t>1:POL.SUPPLIER, 1:PROC.DISPOSAL</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -1390,6 +1479,9 @@
     <t>1º: Riesgo de 1ª parte
 Ex1: Mantener inventarios para todo tipo de hardware, incluidos TI, IoT, OT y dispositivos móviles
 Ex2: Monitoree constantemente las redes para detectar nuevo hardware y actualizar automáticamente los inventarios</t>
+  </si>
+  <si>
+    <t>1:DOC.ASSET_REGISTER, 1:TECH.CMDB, 1:TECH.ASSET_DISCOVERY</t>
   </si>
   <si>
     <t>ID.AM-02</t>
@@ -1420,6 +1512,9 @@
 Ex1: Mantener inventarios para todo tipo de software y servicios, incluidos los comerciales, de código abierto, aplicaciones personalizadas, servicios de API y aplicaciones y servicios basados en la nube
 Ex2: Supervise constantemente todas las plataformas, incluidos los contenedores y las máquinas virtuales, para detectar cambios en el inventario de software y servicios.
 Ex3: Mantener un inventario de los sistemas de la organización</t>
+  </si>
+  <si>
+    <t>1:DOC.ASSET_REGISTER, 1:TECH.CMDB, 1:TECH.SW_INVENTORY</t>
   </si>
   <si>
     <t>ID.AM-03</t>
@@ -1458,6 +1553,9 @@
 Ex4: Mantener la documentación de los puertos de red, protocolos y servicios esperados que se utilizan normalmente entre los sistemas autorizados</t>
   </si>
   <si>
+    <t>1:DOC.FLOW_MATRIX, 1:DOC.IS_MAP</t>
+  </si>
+  <si>
     <t>ID.AM-04</t>
   </si>
   <si>
@@ -1513,6 +1611,9 @@
 Ex1: Definir criterios para priorizar cada clase de activos
 Ex2: Aplicar los criterios de priorización a los activos
 Ex3: Realice un seguimiento de las prioridades de los activos y actualícelas periódicamente o cuando se produzcan cambios significativos en la organización</t>
+  </si>
+  <si>
+    <t>1:POL.CLASSIF, 1:POL.ASSET, 1:DOC.ASSET_REGISTER</t>
   </si>
   <si>
     <t>ID.AM-07</t>
@@ -1546,6 +1647,9 @@
 Ex2: Descubrir y analizar continuamente datos ad hoc para identificar nuevas instancias de tipos de datos designados
 Ex3: Asigne clasificaciones de datos a tipos de datos designados a través de etiquetas o rótulos
 Ex4: Rastree la procedencia, el propietario de los datos y la geolocalización de cada instancia de los tipos de datos designados</t>
+  </si>
+  <si>
+    <t>1:DOC.ASSET_REGISTER, 1:POL.CLASSIF, 1:POL.ASSET</t>
   </si>
   <si>
     <t>ID.AM-08</t>
@@ -1599,6 +1703,9 @@
 Ex9: Ofrecer métodos para destruir papel, medios de almacenamiento y otras formas físicas de almacenamiento de datos.</t>
   </si>
   <si>
+    <t>1:POL.ASSET, 1:PROC.SOFTWARE_LIFECYCLE, 1:PROC.DISPOSAL</t>
+  </si>
+  <si>
     <t>ID.RA</t>
   </si>
   <si>
@@ -1660,6 +1767,9 @@
 Ex6: Revisar los procesos y procedimientos en busca de debilidades que puedan aprovecharse para afectar a la ciberseguridad.</t>
   </si>
   <si>
+    <t>1:POL.VULNERABILITY, 1:TECH.VULN_SCANNER, 1:DOC.RISK_REGISTER</t>
+  </si>
+  <si>
     <t>ID.RA-02</t>
   </si>
   <si>
@@ -1688,6 +1798,9 @@
 Ex1: Configure herramientas y tecnologías de ciberseguridad con capacidades de detección o respuesta para ingerir de forma segura las fuentes de inteligencia de amenazas cibernéticas
 Ex2: Reciba y revise avisos de terceros acreditados sobre los actores de amenazas actuales y sus tácticas, técnicas y procedimientos (TTP)
 Ex3: Monitorear las fuentes de inteligencia de amenazas cibernéticas para obtener información sobre los tipos de vulnerabilidades que pueden tener las tecnologías emergentes</t>
+  </si>
+  <si>
+    <t>1:POL.THREAT_INTEL, 1:PROC.THREAT_INTEL</t>
   </si>
   <si>
     <t>ID.RA-03</t>
@@ -1721,6 +1834,9 @@
 Ex1: Utilice la inteligencia de amenazas cibernéticas para mantener el conocimiento de los tipos de actores de amenazas que probablemente se dirijan a la organización y los TTP que probablemente usarán
 Ex2: Realizar la búsqueda de amenazas para buscar signos de actores de amenazas dentro del entorno
 Ex3: Implementar procesos para identificar a los actores de amenazas internas</t>
+  </si>
+  <si>
+    <t>1:POL.THREAT_INTEL, 1:DOC.RISK_REGISTER</t>
   </si>
   <si>
     <t>ID.RA-04</t>
@@ -1846,6 +1962,9 @@
 Ex4: Revisar periódicamente los riesgos que se aceptaron en función de las acciones o hitos futuros planificados</t>
   </si>
   <si>
+    <t>1:POL.CHANGE_MGMT, 1:PROC.CHANGE_MGMT, 1:PROC.EXCEPTION_MGMT, 1:DOC.EXCEPTION_REGISTER</t>
+  </si>
+  <si>
     <t>ID.RA-08</t>
   </si>
   <si>
@@ -1876,6 +1995,9 @@
 Ex2: Asignar responsabilidades y verificar la ejecución de procedimientos para procesar, analizar el impacto y responder a las divulgaciones de amenazas, vulnerabilidades o incidentes de ciberseguridad por parte de proveedores, clientes, socios y organizaciones gubernamentales de ciberseguridad</t>
   </si>
   <si>
+    <t>1:PROC.VULN_DISCLOSURE, 1:POL.VULNERABILITY</t>
+  </si>
+  <si>
     <t>ID.RA-09</t>
   </si>
   <si>
@@ -1898,6 +2020,9 @@
   <si>
     <t>Ex1: Evaluar la autenticidad y la ciberseguridad de los productos y servicios tecnológicos críticos antes de su adquisición y uso
 3º: Riesgo de 3ª parte</t>
+  </si>
+  <si>
+    <t>1:PROC.TPRM_ASSESSMENT, 1:POL.SUPPLIER, 1:PROC.SBOM</t>
   </si>
   <si>
     <t>ID.RA-10</t>
@@ -1970,6 +2095,9 @@
 Ex1: Realizar autoevaluaciones de los servicios críticos que tengan en cuenta las amenazas actuales y los TTP
 Ex2: Invertir en evaluaciones de terceros o auditorías independientes de la eficacia del programa de ciberseguridad de la organización para identificar las áreas que necesitan mejoras.
 Ex3: Evaluar constantemente el cumplimiento de los requisitos de ciberseguridad seleccionados a través de medios automatizados</t>
+  </si>
+  <si>
+    <t>1:POL.AUDIT, 1:DOC.NC_LOG, 1:DOC.MGMT_REVIEW</t>
   </si>
   <si>
     <t>ID.IM-02</t>
@@ -2014,6 +2142,9 @@
 Ex6: Recopilar y analizar métricas de rendimiento utilizando herramientas y servicios de seguridad para informar sobre las mejoras en el programa de ciberseguridad</t>
   </si>
   <si>
+    <t>1:POL.PENTEST, 1:PROC.BCP_EXERCISE, 1:PROC.IR_EXERCISE</t>
+  </si>
+  <si>
     <t>ID.IM-03</t>
   </si>
   <si>
@@ -2042,6 +2173,9 @@
 Ex1: Llevar a cabo sesiones colaborativas de lecciones aprendidas con los proveedores
 Ex2: Revisar anualmente las políticas, procesos y procedimientos de ciberseguridad para tener en cuenta las lecciones aprendidas.
 Ex3: Utilice métricas para evaluar el rendimiento de la ciberseguridad operativa a lo largo del tiempo</t>
+  </si>
+  <si>
+    <t>1:DOC.NC_LOG, 1:POL.AUDIT</t>
   </si>
   <si>
     <t>ID.IM-04</t>
@@ -2080,6 +2214,9 @@
 Ex5: Revisar y actualizar todos los planes de ciberseguridad anualmente o cuando se identifique la necesidad de mejoras significativas.</t>
   </si>
   <si>
+    <t>1:POL.INCIDENT, 1:PROC.INCIDENT, 1:POL.BCP</t>
+  </si>
+  <si>
     <t>PR</t>
   </si>
   <si>
@@ -2155,6 +2292,9 @@
 Ex4: Etiquete físicamente el hardware autorizado con un identificador para fines de inventario y servicio</t>
   </si>
   <si>
+    <t>1:POL.ACCESS, 1:TECH.IAM</t>
+  </si>
+  <si>
     <t>PR.AA-02</t>
   </si>
   <si>
@@ -2218,6 +2358,9 @@
 Punto 4: Garantizar que el personal autorizado pueda acceder a las cuentas esenciales para proteger la seguridad en condiciones de emergencia</t>
   </si>
   <si>
+    <t>1:POL.ACCESS, 1:TECH.IAM, 1:TECH.MFA</t>
+  </si>
+  <si>
     <t>PR.AA-04</t>
   </si>
   <si>
@@ -2281,6 +2424,9 @@
 Ex4: Revisar periódicamente los privilegios asociados con las funciones críticas del negocio para confirmar la separación adecuada de funciones</t>
   </si>
   <si>
+    <t>1:POL.ACCESS, 1:POL.SEG_DUTY, 1:PROC.RBAC, 1:PROC.RECERTIFICATION</t>
+  </si>
+  <si>
     <t>PR.AA-06</t>
   </si>
   <si>
@@ -2312,6 +2458,9 @@
 Ex1: Use guardias de seguridad, cámaras de seguridad, entradas cerradas, sistemas de alarma y otros controles físicos para monitorear las instalaciones y restringir el acceso
 Ex2: Emplear controles de seguridad física adicionales para áreas que contienen activos de alto riesgo
 Ex3: Acompañe a invitados, proveedores y otros terceros dentro de áreas que contengan activos críticos para el negocio</t>
+  </si>
+  <si>
+    <t>1:PHYS.SECURE_AREA, 1:PHYS.VISITOR_MGMT, 1:POL.PHYSICAL</t>
   </si>
   <si>
     <t>PR.AT</t>
@@ -2371,6 +2520,9 @@
 Ex5: Exigir un repaso anual para reforzar las prácticas existentes e introducir nuevas prácticas</t>
   </si>
   <si>
+    <t>1:POL.EDUC, 1:DOC.EDUC_PLAN, 1:DOC.EDUC_REGISTER</t>
+  </si>
+  <si>
     <t>PR.AT-02</t>
   </si>
   <si>
@@ -2407,6 +2559,9 @@
 Ex4: Exigir un repaso anual para reforzar las prácticas existentes e introducir nuevas prácticas</t>
   </si>
   <si>
+    <t>1:POL.EDUC, 1:DOC.EDUC_PLAN, 1:DOC.COMPETENCY</t>
+  </si>
+  <si>
     <t>PR.DS</t>
   </si>
   <si>
@@ -2464,6 +2619,9 @@
 Ex5: Medios extraíbles físicamente seguros que contienen información confidencial sin cifrar, como dentro de oficinas o archivadores cerrados con llave</t>
   </si>
   <si>
+    <t>1:POL.CRYPTO, 1:TECH.DISK_ENCRYPTION, 1:TECH.FILE_ENCRYPTION</t>
+  </si>
+  <si>
     <t>PR.DS-02</t>
   </si>
   <si>
@@ -2497,6 +2655,9 @@
 Ex4: Evitar la reutilización de datos confidenciales de entornos de producción (por ejemplo, registros de clientes) en entornos de desarrollo, pruebas y otros entornos que no sean de producción</t>
   </si>
   <si>
+    <t>1:POL.CRYPTO, 1:POL.TRANSFER, 1:TECH.VPN</t>
+  </si>
+  <si>
     <t>PR.DS-10</t>
   </si>
   <si>
@@ -2522,6 +2683,9 @@
     <t>1º: Riesgo de 1ª parte
 Ex1: Eliminar los datos que deben permanecer confidenciales (por ejemplo, de los procesadores y la memoria) tan pronto como ya no sean necesarios
 Ex2: Proteger los datos en uso del acceso de otros usuarios y procesos de la misma plataforma</t>
+  </si>
+  <si>
+    <t>1:POL.CRYPTO, 1:TECH.DLP</t>
   </si>
   <si>
     <t>PR.DS-11</t>
@@ -2557,6 +2721,9 @@
 Ex4: Aplicar restricciones de separación geográfica y geolocalización para el almacenamiento de copias de seguridad de datos</t>
   </si>
   <si>
+    <t>1:POL.BACKUP, 1:TECH.IMMUTABLE_BACKUP, 1:PROC.BCP_EXERCISE</t>
+  </si>
+  <si>
     <t>PR.PS</t>
   </si>
   <si>
@@ -2606,6 +2773,9 @@
 Ex1: Establecer, probar, implementar y mantener líneas de base reforzadas que hagan cumplir las políticas de ciberseguridad de la organización y proporcionen solo capacidades esenciales (es decir, el principio de funcionalidad mínima)
 Ex2: Revise todos los ajustes de configuración predeterminados que puedan afectar a la ciberseguridad al instalar o actualizar software
 Ex3: Supervisar el software implementado para detectar desviaciones de las líneas de base aprobadas</t>
+  </si>
+  <si>
+    <t>1:POL.HARDENING, 1:PROC.GPO, 1:PROC.CHANGE_MGMT</t>
   </si>
   <si>
     <t>PR.PS-02</t>
@@ -2647,6 +2817,9 @@
 Ex6: Definir e implementar planes para el soporte de mantenimiento al final de la vida útil del software y los servicios y la obsolescencia</t>
   </si>
   <si>
+    <t>1:PROC.SOFTWARE_LIFECYCLE, 1:PROC.UPDATE, 1:POL.MAINTENANCE</t>
+  </si>
+  <si>
     <t>PR.PS-03</t>
   </si>
   <si>
@@ -2680,6 +2853,9 @@
 Ex3: Realizar la eliminación de hardware de forma segura, responsable y auditable</t>
   </si>
   <si>
+    <t>1:POL.MAINTENANCE, 1:PROC.DISPOSAL, 1:POL.ASSET</t>
+  </si>
+  <si>
     <t>PR.PS-04</t>
   </si>
   <si>
@@ -2708,6 +2884,9 @@
 Ex1: Configurar todos los sistemas operativos, aplicaciones y servicios (incluidos los servicios basados en la nube) para generar registros
 Ex2: Configurar generadores de registros para compartir de forma segura sus registros con los sistemas y servicios de infraestructura de registro de la organización
 Ex3: Configurar generadores de registros para registrar los datos que necesitan las arquitecturas de confianza cero</t>
+  </si>
+  <si>
+    <t>1:PROC.LOGGING, 1:POL.MONITOR, 1:TECH.ACCESS_LOG</t>
   </si>
   <si>
     <t>PR.PS-05</t>
@@ -2743,6 +2922,9 @@
 Ex4: Configurar plataformas para permitir la instalación solo de software aprobado por la organización</t>
   </si>
   <si>
+    <t>1:POL.APP_CONTROL, 1:TECH.APP_CONTROL</t>
+  </si>
+  <si>
     <t>PR.PS-06</t>
   </si>
   <si>
@@ -2771,6 +2953,9 @@
 Ex1: Proteger todos los componentes del software desarrollado por la organización contra la manipulación y el acceso no autorizado
 Ex2: Asegurar todo el software producido por la organización, con vulnerabilidades mínimas en sus versiones
 Ex3: Mantener el software utilizado en los entornos de producción y desechar de forma segura el software una vez que ya no sea necesario</t>
+  </si>
+  <si>
+    <t>1:POL.SECDEV, 1:PROC.SDLC, 1:TECH.SAST_DAST</t>
   </si>
   <si>
     <t>PR.IR</t>
@@ -2830,6 +3015,9 @@
 Ex4: Comprobar el estado cibernético de los endpoints antes de permitirles acceder y utilizar los recursos de producción</t>
   </si>
   <si>
+    <t>1:POL.NETWORK, 1:TECH.NETWORK_FIREWALL, 1:TECH.VLAN, 1:TECH.MICROSEGMENTATION</t>
+  </si>
+  <si>
     <t>PR.IR-02</t>
   </si>
   <si>
@@ -2860,6 +3048,9 @@
 Ex2: Incluir la protección contra las amenazas ambientales y las disposiciones para una infraestructura operativa adecuada en los requisitos para los proveedores de servicios que operan sistemas en nombre de la organización.</t>
   </si>
   <si>
+    <t>1:POL.PHYSICAL, 1:PHYS.POWER_ENV, 1:PHYS.SECURE_AREA</t>
+  </si>
+  <si>
     <t>PR.IR-03</t>
   </si>
   <si>
@@ -2890,6 +3081,9 @@
 Ex3: Utilice componentes de alta disponibilidad, como almacenamiento redundante y fuentes de alimentación, para mejorar la fiabilidad del sistema</t>
   </si>
   <si>
+    <t>1:POL.BCP, 1:TECH.DR_SITE</t>
+  </si>
+  <si>
     <t>PR.IR-04</t>
   </si>
   <si>
@@ -2912,6 +3106,9 @@
   <si>
     <t>Ex1: Supervise el uso del almacenamiento, la energía, la computación, el ancho de banda de red y otros recursos
 Ex2: Pronostique las necesidades futuras y escale los recursos en consecuencia</t>
+  </si>
+  <si>
+    <t>1:PROC.CAPACITY_MGMT</t>
   </si>
   <si>
     <t>DE</t>
@@ -2992,6 +3189,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:TECH.SIEM, 1:TECH.IDS, 1:POL.MONITOR, 1:PROC.LOGGING</t>
+  </si>
+  <si>
     <t>DE.CM-02</t>
   </si>
   <si>
@@ -3025,6 +3225,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:PHYS.CCTV, 1:PHYS.SECURE_AREA</t>
+  </si>
+  <si>
     <t>DE.CM-03</t>
   </si>
   <si>
@@ -3055,6 +3258,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:TECH.ACCESS_LOG, 1:TECH.DLP, 1:PROC.INSIDER_THREAT</t>
+  </si>
+  <si>
     <t>DE.CM-06</t>
   </si>
   <si>
@@ -3080,6 +3286,9 @@
     <t>Ex1: Supervisar las actividades de administración y mantenimiento remotas e in situ que los proveedores externos realizan en los sistemas de la organización
 Ex2: Supervise la actividad de los servicios basados en la nube, los proveedores de servicios de Internet y otros proveedores de servicios para detectar desviaciones del comportamiento esperado
 3º: Riesgo de 3ª parte</t>
+  </si>
+  <si>
+    <t>1:POL.SUPPLIER, 1:TECH.SIEM, 1:PROC.TPRM_ASSESSMENT</t>
   </si>
   <si>
     <t>DE.CM-09</t>
@@ -3118,6 +3327,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:TECH.EDR, 1:TECH.SIEM, 1:TECH.CMDB</t>
+  </si>
+  <si>
     <t>DE.AE</t>
   </si>
   <si>
@@ -3172,6 +3384,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:TECH.SIEM, 1:PROC.THREAT_HUNT, 1:POL.MONITOR</t>
+  </si>
+  <si>
     <t>DE.AE-03</t>
   </si>
   <si>
@@ -3202,6 +3417,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:TECH.SIEM, 1:PROC.LOGGING</t>
+  </si>
+  <si>
     <t>DE.AE-04</t>
   </si>
   <si>
@@ -3227,6 +3445,9 @@
     <t>Ex1: Utilice SIEM u otras herramientas para estimar el impacto y el alcance, y revise y perfeccione las estimaciones
 Ex2: Una persona crea sus propias estimaciones de impacto y alcance
 1º: Riesgo de 1ª parte</t>
+  </si>
+  <si>
+    <t>1:PROC.INCIDENT, 1:TECH.SIEM</t>
   </si>
   <si>
     <t>DE.AE-06</t>
@@ -3262,6 +3483,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:TECH.SIEM, 1:PROC.INCIDENT, 1:POL.MONITOR</t>
+  </si>
+  <si>
     <t>DE.AE-07</t>
   </si>
   <si>
@@ -3292,6 +3516,9 @@
 1º: Riesgo de 1ª parte</t>
   </si>
   <si>
+    <t>1:POL.THREAT_INTEL, 1:PROC.THREAT_INTEL, 1:TECH.SIEM</t>
+  </si>
+  <si>
     <t>DE.AE-08</t>
   </si>
   <si>
@@ -3317,6 +3544,9 @@
     <t>Ex1: Aplicar criterios de incidente a las características conocidas y supuestas de la actividad para determinar si un incidente debe declararse
 Ex2: Tener en cuenta los falsos positivos conocidos al aplicar los criterios de incidentes
 1º: Riesgo de 1ª parte</t>
+  </si>
+  <si>
+    <t>1:POL.INCIDENT, 1:PROC.INCIDENT</t>
   </si>
   <si>
     <t>RS</t>
@@ -3394,6 +3624,9 @@
 3º: Riesgo de 3ª parte</t>
   </si>
   <si>
+    <t>1:POL.INCIDENT, 1:PROC.INCIDENT, 1:POL.SUPPLIER</t>
+  </si>
+  <si>
     <t>RS.MA-02</t>
   </si>
   <si>
@@ -3419,6 +3652,9 @@
     <t>1º: Riesgo de 1ª parte
 Ex1: Revisar preliminarmente los informes de incidentes para confirmar que están relacionados con la ciberseguridad y requieren actividades de respuesta a incidentes.
 Ex2: Aplicar criterios para estimar la gravedad de un incidente</t>
+  </si>
+  <si>
+    <t>1:PROC.INCIDENT, 1:DOC.INCIDENT_REGISTER</t>
   </si>
   <si>
     <t>RS.MA-03</t>
@@ -3451,6 +3687,9 @@
 Ex3: seleccione estrategias de respuesta a incidentes para incidentes activos equilibrando la necesidad de recuperarse rápidamente de un incidente con la necesidad de observar al atacante o realizar una investigación más exhaustiva</t>
   </si>
   <si>
+    <t>1:PROC.INCIDENT, 1:POL.INCIDENT</t>
+  </si>
+  <si>
     <t>RS.MA-04</t>
   </si>
   <si>
@@ -3478,6 +3717,9 @@
 Ex2: Coordinar la escalada o elevación de incidentes con las partes interesadas internas y externas designadas</t>
   </si>
   <si>
+    <t>1:PROC.INCIDENT, 1:PROC.CRISIS_MGMT</t>
+  </si>
+  <si>
     <t>RS.MA-05</t>
   </si>
   <si>
@@ -3503,6 +3745,9 @@
     <t>1º: Riesgo de 1ª parte
 Ex1: Aplicar criterios de recuperación de incidentes a las características conocidas y supuestas del incidente para determinar si se deben iniciar procesos de recuperación de incidentes
 Ex2: Tener en cuenta la posible interrupción operativa de las actividades de recuperación de incidentes</t>
+  </si>
+  <si>
+    <t>1:PROC.INCIDENT, 1:PROC.DRP</t>
   </si>
   <si>
     <t>RS.AN</t>
@@ -3559,6 +3804,9 @@
 Ex4: Compruebe cualquier tecnología de engaño cibernético para obtener información adicional sobre el comportamiento del atacante</t>
   </si>
   <si>
+    <t>1:PROC.INCIDENT, 1:PROC.FORENSICS, 1:PROC.POST_INCIDENT</t>
+  </si>
+  <si>
     <t>RS.AN-06</t>
   </si>
   <si>
@@ -3586,6 +3834,9 @@
 Ex2: Exigir al líder del incidente que documente el incidente en detalle y sea responsable de preservar la integridad de la documentación y las fuentes de toda la información que se informa.</t>
   </si>
   <si>
+    <t>1:PROC.FORENSICS</t>
+  </si>
+  <si>
     <t>RS.AN-07</t>
   </si>
   <si>
@@ -3608,6 +3859,9 @@
   <si>
     <t>1º: Riesgo de 1ª parte
 Ex1: Recopilar, preservar y salvaguardar la integridad de todos los datos y metadatos pertinentes del incidente (por ejemplo, fuente de datos, fecha/hora de recopilación) en función de los procedimientos de preservación de pruebas y cadena de custodia</t>
+  </si>
+  <si>
+    <t>1:PROC.FORENSICS, 1:PROC.LOGGING</t>
   </si>
   <si>
     <t>RS.AN-08</t>
@@ -3689,6 +3943,9 @@
 Ex1: Siga los procedimientos de notificación de infracciones de la organización después de descubrir un incidente de infracción de datos, incluida la notificación a los clientes afectados
 Ex2: Notificar a los socios comerciales y clientes de los incidentes de acuerdo con los requisitos contractuales
 Ex3: Notificar a las agencias de aplicación de la ley y a los organismos reguladores de los incidentes en función de los criterios del plan de respuesta a incidentes y la aprobación de la dirección.</t>
+  </si>
+  <si>
+    <t>1:PROC.INCIDENT, 1:DOC.COM, 1:PROC.BREACH_NOTIF</t>
   </si>
   <si>
     <t>RS.CO-03</t>
@@ -3733,6 +3990,9 @@
 Ex6: Coordinar los métodos de comunicación de crisis entre la organización y sus proveedores críticos</t>
   </si>
   <si>
+    <t>1:PROC.INCIDENT, 1:DOC.COM</t>
+  </si>
+  <si>
     <t>RS.MI</t>
   </si>
   <si>
@@ -3790,6 +4050,9 @@
 Ex4: Transfiera automáticamente los puntos de conexión comprometidos a una red de área local virtual (VLAN) de corrección</t>
   </si>
   <si>
+    <t>1:PROC.INCIDENT, 1:TECH.EDR, 1:TECH.NETWORK_FIREWALL</t>
+  </si>
+  <si>
     <t>RS.MI-02</t>
   </si>
   <si>
@@ -3823,6 +4086,9 @@
 Ex3: Permitir que un tercero (por ejemplo, un proveedor de servicios de seguridad administrados) realice acciones de erradicación en nombre de la organización.</t>
   </si>
   <si>
+    <t>1:PROC.INCIDENT, 1:TECH.EDR</t>
+  </si>
+  <si>
     <t>RC</t>
   </si>
   <si>
@@ -3892,6 +4158,9 @@
 Ex2: Informar a todas las personas con responsabilidades de recuperación de los planes de recuperación y de las autorizaciones necesarias para implementar cada aspecto de los planes</t>
   </si>
   <si>
+    <t>1:PROC.DRP, 1:POL.BCP, 1:PROC.INCIDENT</t>
+  </si>
+  <si>
     <t>RC.RP-02</t>
   </si>
   <si>
@@ -3919,6 +4188,9 @@
 Ex2: Cambiar las acciones de recuperación planificadas en función de una reevaluación de las necesidades y los recursos de la organización</t>
   </si>
   <si>
+    <t>1:PROC.DRP, 1:POL.BCP</t>
+  </si>
+  <si>
     <t>RC.RP-03</t>
   </si>
   <si>
@@ -3941,6 +4213,9 @@
   <si>
     <t>1º: Riesgo de 1ª parte
 Ex1: Compruebe los activos de restauración en busca de indicadores de compromiso, daños en los archivos y otros problemas de integridad antes de su uso</t>
+  </si>
+  <si>
+    <t>1:POL.BACKUP, 1:TECH.IMMUTABLE_BACKUP, 1:PROC.DRP</t>
   </si>
   <si>
     <t>RC.RP-04</t>
@@ -3973,6 +4248,9 @@
 Ex3: Supervisar el rendimiento de los sistemas restaurados para verificar la idoneidad de la restauración</t>
   </si>
   <si>
+    <t>1:POL.BCP, 1:DOC.BIA</t>
+  </si>
+  <si>
     <t>RC.RP-05</t>
   </si>
   <si>
@@ -4000,6 +4278,9 @@
 Ex2: Verificar la exactitud y adecuación de las acciones de restauración realizadas antes de poner en línea un sistema restaurado</t>
   </si>
   <si>
+    <t>1:PROC.DRP, 1:POL.BACKUP</t>
+  </si>
+  <si>
     <t>RC.RP-06</t>
   </si>
   <si>
@@ -4025,6 +4306,9 @@
     <t>1º: Riesgo de 1ª parte
 Ex1: Prepare un informe posterior a la acción que documente el incidente en sí, las acciones de respuesta y recuperación tomadas, y las lecciones aprendidas
 Ex2: Declarar el fin de la recuperación de incidentes una vez que se cumplan los criterios</t>
+  </si>
+  <si>
+    <t>1:PROC.DRP, 1:PROC.POST_INCIDENT</t>
   </si>
   <si>
     <t>RC.CO</t>
@@ -4084,6 +4368,9 @@
 Ex4: Coordinar la comunicación de crisis entre la organización y sus proveedores críticos</t>
   </si>
   <si>
+    <t>1:DOC.COM, 1:PROC.CRISIS_MGMT, 1:PROC.INCIDENT</t>
+  </si>
+  <si>
     <t>RC.CO-04</t>
   </si>
   <si>
@@ -4111,6 +4398,9 @@
 Ex2: Explique los pasos que se están tomando para recuperarse del incidente y evitar que se repita</t>
   </si>
   <si>
+    <t>1:DOC.COM, 1:PROC.CRISIS_MGMT</t>
+  </si>
+  <si>
     <t>score</t>
   </si>
   <si>
@@ -4193,6 +4483,27 @@
   </si>
   <si>
     <t>Existe un enfoque de toda la organización para gestionar los riesgos de ciberseguridad que utiliza políticas, procesos y procedimientos informados sobre el riesgo para abordar posibles eventos de ciberseguridad. La organización adapta sus prácticas de ciberseguridad en función de las actividades de ciberseguridad anteriores y actuales, incluidas las lecciones aprendidas y los indicadores predictivos.</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>urn_prefix</t>
+  </si>
+  <si>
+    <t>prefix_id</t>
+  </si>
+  <si>
+    <t>prefix_value</t>
+  </si>
+  <si>
+    <t>urn:intuitem:risk:function:doc-pol</t>
+  </si>
+  <si>
+    <t>dependencies</t>
+  </si>
+  <si>
+    <t>urn:intuitem:risk:library:doc-pol</t>
   </si>
 </sst>
 </file>
@@ -4273,7 +4584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4301,6 +4612,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4603,7 +4917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -4630,96 +4944,104 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10">
-        <v>5</v>
+      <c r="B3" s="10" t="s">
+        <v>1100</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
@@ -4741,15 +5063,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -4757,47 +5079,47 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -4815,24 +5137,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="129.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" customWidth="1"/>
-    <col min="8" max="8" width="62" style="1" customWidth="1"/>
-    <col min="9" max="9" width="63" customWidth="1"/>
-    <col min="10" max="10" width="24.77734375" customWidth="1"/>
-    <col min="11" max="11" width="66" style="1" customWidth="1"/>
-    <col min="12" max="12" width="65.6640625" customWidth="1"/>
+    <col min="7" max="7" width="35" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" customWidth="1"/>
+    <col min="9" max="9" width="62" style="1" customWidth="1"/>
+    <col min="10" max="10" width="63" customWidth="1"/>
+    <col min="11" max="11" width="24.77734375" customWidth="1"/>
+    <col min="12" max="12" width="66" style="1" customWidth="1"/>
+    <col min="13" max="13" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -4840,3836 +5163,4157 @@
         <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>45</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="L2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="L3" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="M4" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="J5" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="L5" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="I15" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>137</v>
+        <v>146</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>151</v>
+        <v>160</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>193</v>
+        <v>206</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>198</v>
+        <v>213</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D25" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>207</v>
+        <v>222</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>212</v>
+        <v>228</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>214</v>
+        <v>229</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>221</v>
+        <v>237</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D29" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30">
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>240</v>
+        <v>259</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>242</v>
+        <v>260</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B31">
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>247</v>
+        <v>267</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>249</v>
+        <v>268</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>254</v>
+        <v>275</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>256</v>
+        <v>276</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>261</v>
+        <v>283</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>263</v>
+        <v>284</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>268</v>
+        <v>291</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>270</v>
+        <v>292</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>275</v>
+        <v>299</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>277</v>
+        <v>300</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>282</v>
+        <v>307</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>284</v>
+        <v>308</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37">
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>289</v>
+        <v>315</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>291</v>
+        <v>316</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="H38" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>296</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>298</v>
+        <v>324</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>303</v>
+        <v>330</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>305</v>
+        <v>331</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>312</v>
+        <v>339</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="D41" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>319</v>
+        <v>346</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>324</v>
+        <v>352</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>326</v>
+        <v>353</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>331</v>
+        <v>360</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>333</v>
+        <v>361</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>338</v>
+        <v>368</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>340</v>
+        <v>369</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>345</v>
+        <v>376</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>347</v>
+        <v>377</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>352</v>
+        <v>383</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>354</v>
+        <v>384</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>359</v>
+        <v>391</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>361</v>
+        <v>392</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>366</v>
+        <v>399</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>368</v>
+        <v>400</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>370</v>
+        <v>405</v>
       </c>
       <c r="D49" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>375</v>
+        <v>408</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>378</v>
+        <v>413</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>380</v>
+        <v>414</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>382</v>
+        <v>415</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>387</v>
+        <v>422</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>389</v>
+        <v>423</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>424</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>394</v>
+        <v>430</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>435</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>396</v>
+        <v>431</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>432</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>401</v>
+        <v>438</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>403</v>
+        <v>439</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>408</v>
+        <v>445</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>410</v>
+        <v>446</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>415</v>
+        <v>452</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>417</v>
+        <v>453</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>454</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>422</v>
+        <v>459</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>424</v>
+        <v>460</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>429</v>
+        <v>467</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>472</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>431</v>
+        <v>468</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>436</v>
+        <v>475</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>438</v>
+        <v>476</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>477</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>478</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>443</v>
+        <v>483</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>445</v>
+        <v>484</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>486</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="D60" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>452</v>
+        <v>491</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>492</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>493</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>455</v>
+        <v>496</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>457</v>
+        <v>497</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>502</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>459</v>
+        <v>498</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B62">
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>462</v>
+        <v>504</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>464</v>
+        <v>505</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>466</v>
+        <v>506</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>468</v>
+        <v>511</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>469</v>
+        <v>512</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>471</v>
+        <v>513</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>518</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>473</v>
+        <v>514</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>515</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>475</v>
+        <v>519</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>476</v>
+        <v>520</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>478</v>
+        <v>521</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>526</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>480</v>
+        <v>522</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>523</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>482</v>
+        <v>527</v>
       </c>
       <c r="D65" t="s">
-        <v>483</v>
+        <v>528</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>485</v>
+        <v>529</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>531</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="D66" t="s">
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>492</v>
+        <v>536</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>494</v>
+        <v>537</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B67">
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>499</v>
+        <v>543</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>548</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>501</v>
+        <v>544</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>545</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>503</v>
+        <v>549</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>504</v>
+        <v>550</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>506</v>
+        <v>551</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>548</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>508</v>
+        <v>552</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>510</v>
+        <v>556</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>511</v>
+        <v>557</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>513</v>
+        <v>558</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>563</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>515</v>
+        <v>559</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B70">
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>517</v>
+        <v>564</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>518</v>
+        <v>565</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>520</v>
+        <v>566</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>563</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>522</v>
+        <v>567</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>568</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B71">
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>524</v>
+        <v>571</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>527</v>
+        <v>573</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>578</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>529</v>
+        <v>574</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>576</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>531</v>
+        <v>579</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>532</v>
+        <v>580</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>534</v>
+        <v>581</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>586</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>536</v>
+        <v>582</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>583</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>584</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>538</v>
+        <v>587</v>
       </c>
       <c r="D73" t="s">
-        <v>539</v>
+        <v>588</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>541</v>
+        <v>589</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>543</v>
+        <v>590</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>591</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+        <v>592</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B74">
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>545</v>
+        <v>594</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>546</v>
+        <v>595</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>548</v>
+        <v>596</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>601</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>550</v>
+        <v>597</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>598</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>552</v>
+        <v>602</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>553</v>
+        <v>603</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>555</v>
+        <v>604</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>609</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>557</v>
+        <v>605</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>606</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>559</v>
+        <v>610</v>
       </c>
       <c r="D76" t="s">
-        <v>560</v>
+        <v>611</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>562</v>
+        <v>612</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>564</v>
+        <v>613</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>614</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>615</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B77">
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>567</v>
+        <v>618</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>569</v>
+        <v>619</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>571</v>
+        <v>620</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>621</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>573</v>
+        <v>625</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>574</v>
+        <v>626</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>576</v>
+        <v>627</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>632</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>578</v>
+        <v>628</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>629</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>630</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B79">
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>580</v>
+        <v>633</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>583</v>
+        <v>635</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>640</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>585</v>
+        <v>636</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>637</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>638</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>587</v>
+        <v>641</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>590</v>
+        <v>643</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>648</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>592</v>
+        <v>644</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>645</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>594</v>
+        <v>649</v>
       </c>
       <c r="D81" t="s">
-        <v>595</v>
+        <v>650</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>597</v>
+        <v>651</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>599</v>
+        <v>652</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>654</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B82">
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>601</v>
+        <v>656</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>602</v>
+        <v>657</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>604</v>
+        <v>658</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>663</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>606</v>
+        <v>659</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+        <v>661</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B83">
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>608</v>
+        <v>664</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>609</v>
+        <v>665</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>611</v>
+        <v>666</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>671</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>613</v>
+        <v>667</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>668</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>615</v>
+        <v>672</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>616</v>
+        <v>673</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>618</v>
+        <v>674</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>679</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>620</v>
+        <v>675</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>676</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>677</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B85">
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>622</v>
+        <v>680</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>623</v>
+        <v>681</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>625</v>
+        <v>682</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>687</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>627</v>
+        <v>683</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>684</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>685</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>629</v>
+        <v>688</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>630</v>
+        <v>689</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>632</v>
+        <v>690</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>695</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>634</v>
+        <v>691</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>692</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>693</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B87">
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>636</v>
+        <v>696</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>637</v>
+        <v>697</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>639</v>
+        <v>698</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>703</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>641</v>
+        <v>699</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>700</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>701</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88" t="s">
-        <v>643</v>
+        <v>704</v>
       </c>
       <c r="D88" t="s">
-        <v>644</v>
+        <v>705</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>646</v>
+        <v>706</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>648</v>
+        <v>707</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>708</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>709</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B89">
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>650</v>
+        <v>711</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>651</v>
+        <v>712</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>653</v>
+        <v>713</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>718</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>655</v>
+        <v>714</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>715</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>716</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B90">
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>657</v>
+        <v>719</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>660</v>
+        <v>721</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>726</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>662</v>
+        <v>722</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>723</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>664</v>
+        <v>727</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>665</v>
+        <v>728</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>667</v>
+        <v>729</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>734</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>669</v>
+        <v>730</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>731</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>671</v>
+        <v>735</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>672</v>
+        <v>736</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>674</v>
+        <v>737</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>742</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>676</v>
+        <v>738</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>739</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>740</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>678</v>
+        <v>743</v>
       </c>
       <c r="D93" t="s">
-        <v>679</v>
+        <v>744</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>681</v>
+        <v>745</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>683</v>
+        <v>746</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>747</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>748</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>685</v>
+        <v>750</v>
       </c>
       <c r="D94" t="s">
-        <v>686</v>
+        <v>751</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>688</v>
+        <v>752</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>690</v>
+        <v>753</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>754</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B95">
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>692</v>
+        <v>757</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>693</v>
+        <v>758</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>695</v>
+        <v>759</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>764</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>697</v>
+        <v>760</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>761</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+        <v>762</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>699</v>
+        <v>765</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>700</v>
+        <v>766</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>702</v>
+        <v>767</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>772</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>704</v>
+        <v>768</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>769</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+        <v>770</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B97">
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>706</v>
+        <v>773</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>707</v>
+        <v>774</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>709</v>
+        <v>775</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>780</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>711</v>
+        <v>776</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>777</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+        <v>778</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B98">
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>713</v>
+        <v>781</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>714</v>
+        <v>782</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>716</v>
+        <v>783</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>788</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>718</v>
+        <v>784</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>785</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+        <v>786</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B99">
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>720</v>
+        <v>789</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>721</v>
+        <v>790</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>723</v>
+        <v>791</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>796</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>725</v>
+        <v>792</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>793</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>2</v>
       </c>
       <c r="C100" t="s">
-        <v>727</v>
+        <v>797</v>
       </c>
       <c r="D100" t="s">
-        <v>728</v>
+        <v>798</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>730</v>
+        <v>799</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>732</v>
+        <v>800</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>801</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>802</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B101">
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>734</v>
+        <v>804</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>735</v>
+        <v>805</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>737</v>
+        <v>806</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>811</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>739</v>
+        <v>807</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>808</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+        <v>809</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B102">
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>741</v>
+        <v>812</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>742</v>
+        <v>813</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>744</v>
+        <v>814</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>819</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>746</v>
+        <v>815</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>816</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>817</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B103">
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>748</v>
+        <v>820</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>749</v>
+        <v>821</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>751</v>
+        <v>822</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>827</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>753</v>
+        <v>823</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>824</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+        <v>825</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>755</v>
+        <v>828</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>756</v>
+        <v>829</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>758</v>
+        <v>830</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>835</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>760</v>
+        <v>831</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>832</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>833</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B105">
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>762</v>
+        <v>836</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>763</v>
+        <v>837</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>765</v>
+        <v>838</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>843</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>767</v>
+        <v>839</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>840</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>841</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B106">
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>769</v>
+        <v>844</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>770</v>
+        <v>845</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>772</v>
+        <v>846</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>851</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>774</v>
+        <v>847</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>848</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>849</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>776</v>
+        <v>852</v>
       </c>
       <c r="D107" t="s">
-        <v>777</v>
+        <v>853</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>779</v>
+        <v>854</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>781</v>
+        <v>855</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>856</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>857</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108" t="s">
-        <v>783</v>
+        <v>859</v>
       </c>
       <c r="D108" t="s">
-        <v>784</v>
+        <v>860</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>786</v>
+        <v>861</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>788</v>
+        <v>862</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>863</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+        <v>864</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B109">
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>790</v>
+        <v>866</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>791</v>
+        <v>867</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>793</v>
+        <v>868</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>873</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>795</v>
+        <v>869</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>870</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>871</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B110">
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>797</v>
+        <v>874</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>798</v>
+        <v>875</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>800</v>
+        <v>876</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>881</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>802</v>
+        <v>877</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>878</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>879</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B111">
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>804</v>
+        <v>882</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>805</v>
+        <v>883</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>807</v>
+        <v>884</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>889</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>809</v>
+        <v>885</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>886</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+        <v>887</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B112">
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>811</v>
+        <v>890</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>812</v>
+        <v>891</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>814</v>
+        <v>892</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>897</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>816</v>
+        <v>893</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>894</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>895</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B113">
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>818</v>
+        <v>898</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>819</v>
+        <v>899</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>821</v>
+        <v>900</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>905</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>823</v>
+        <v>901</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>902</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>903</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114" t="s">
-        <v>825</v>
+        <v>906</v>
       </c>
       <c r="D114" t="s">
-        <v>826</v>
+        <v>907</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>55</v>
+      </c>
+      <c r="B115">
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>913</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>55</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>921</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>55</v>
+      </c>
+      <c r="B117">
+        <v>3</v>
+      </c>
+      <c r="C117" t="s">
+        <v>929</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>55</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118" t="s">
+        <v>937</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="G118" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="G114" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="144" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>54</v>
-      </c>
-      <c r="B115">
-        <v>3</v>
-      </c>
-      <c r="C115" t="s">
-        <v>832</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>54</v>
-      </c>
-      <c r="B116">
-        <v>3</v>
-      </c>
-      <c r="C116" t="s">
-        <v>839</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="72" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>54</v>
-      </c>
-      <c r="B117">
-        <v>3</v>
-      </c>
-      <c r="C117" t="s">
-        <v>846</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="L117" s="1" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="72" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>54</v>
-      </c>
-      <c r="B118">
-        <v>3</v>
-      </c>
-      <c r="C118" t="s">
-        <v>853</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>856</v>
-      </c>
       <c r="I118" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>858</v>
+        <v>940</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>941</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>942</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>860</v>
+        <v>944</v>
       </c>
       <c r="D119" t="s">
-        <v>861</v>
+        <v>945</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>863</v>
+        <v>946</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>865</v>
+        <v>947</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>948</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>949</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>867</v>
+        <v>951</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>868</v>
+        <v>952</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>869</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>870</v>
+        <v>953</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>958</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>872</v>
+        <v>954</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>955</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+        <v>956</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B121">
         <v>3</v>
       </c>
       <c r="C121" t="s">
-        <v>874</v>
+        <v>959</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>875</v>
+        <v>960</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>877</v>
+        <v>961</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>966</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>879</v>
+        <v>962</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>963</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>964</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>2</v>
       </c>
       <c r="C122" t="s">
-        <v>881</v>
+        <v>967</v>
       </c>
       <c r="D122" t="s">
-        <v>882</v>
+        <v>968</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>884</v>
+        <v>969</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>886</v>
+        <v>970</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>971</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+        <v>972</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B123">
         <v>3</v>
       </c>
       <c r="C123" t="s">
-        <v>888</v>
+        <v>974</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>889</v>
+        <v>975</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>891</v>
+        <v>976</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>981</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>893</v>
+        <v>977</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>978</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>979</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B124">
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>895</v>
+        <v>982</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>896</v>
+        <v>983</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>898</v>
+        <v>984</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>989</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>900</v>
+        <v>985</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>986</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>987</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125" t="s">
-        <v>902</v>
+        <v>990</v>
       </c>
       <c r="D125" t="s">
-        <v>903</v>
+        <v>991</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>905</v>
+        <v>992</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>907</v>
+        <v>993</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>994</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>995</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126" t="s">
-        <v>909</v>
+        <v>997</v>
       </c>
       <c r="D126" t="s">
-        <v>910</v>
+        <v>998</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>912</v>
+        <v>999</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>914</v>
+        <v>1000</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>1001</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B127">
         <v>3</v>
       </c>
       <c r="C127" t="s">
-        <v>916</v>
+        <v>1004</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>917</v>
+        <v>1005</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>918</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>919</v>
+        <v>1006</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>1011</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>921</v>
+        <v>1007</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>1008</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>1009</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>923</v>
+        <v>1012</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>924</v>
+        <v>1013</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>926</v>
+        <v>1014</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>1019</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>928</v>
+        <v>1015</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>1016</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+        <v>1017</v>
+      </c>
+      <c r="M128" s="1" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B129">
         <v>3</v>
       </c>
       <c r="C129" t="s">
-        <v>930</v>
+        <v>1020</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>931</v>
+        <v>1021</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>933</v>
+        <v>1022</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>1027</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>934</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>935</v>
+        <v>1023</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>1024</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+        <v>1025</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B130">
         <v>3</v>
       </c>
       <c r="C130" t="s">
-        <v>937</v>
+        <v>1028</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>938</v>
+        <v>1029</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>940</v>
+        <v>1030</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>1035</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>942</v>
+        <v>1031</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>1032</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>1033</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B131">
         <v>3</v>
       </c>
       <c r="C131" t="s">
-        <v>944</v>
+        <v>1036</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>945</v>
+        <v>1037</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>946</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>947</v>
+        <v>1038</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>1043</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>949</v>
+        <v>1039</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>1040</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>1041</v>
+      </c>
+      <c r="M131" s="1" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132" t="s">
-        <v>951</v>
+        <v>1044</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>952</v>
+        <v>1045</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>954</v>
+        <v>1046</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>1051</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>956</v>
+        <v>1047</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>1048</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>1049</v>
+      </c>
+      <c r="M132" s="1" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>2</v>
       </c>
       <c r="C133" t="s">
-        <v>958</v>
+        <v>1052</v>
       </c>
       <c r="D133" t="s">
-        <v>959</v>
+        <v>1053</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>961</v>
+        <v>1054</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>963</v>
+        <v>1055</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>1056</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+        <v>1057</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B134">
         <v>3</v>
       </c>
       <c r="C134" t="s">
-        <v>965</v>
+        <v>1059</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>966</v>
+        <v>1060</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>968</v>
+        <v>1061</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>1066</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>970</v>
+        <v>1062</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>1063</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>1064</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B135">
         <v>3</v>
       </c>
       <c r="C135" t="s">
-        <v>972</v>
+        <v>1067</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>973</v>
+        <v>1068</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>975</v>
+        <v>1069</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>1074</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>976</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>977</v>
+        <v>1070</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>1071</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>978</v>
+        <v>1072</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -8692,7 +9336,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
@@ -8718,117 +9362,117 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>979</v>
+        <v>1075</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="124.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>980</v>
+        <v>1076</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>981</v>
+        <v>1077</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>982</v>
+        <v>1078</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>983</v>
+        <v>1079</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>984</v>
+        <v>1080</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="93.6" x14ac:dyDescent="0.3">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>986</v>
+        <v>1082</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>987</v>
+        <v>1083</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>988</v>
+        <v>1084</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>989</v>
+        <v>1085</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>990</v>
+        <v>1086</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>992</v>
+        <v>1088</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>993</v>
+        <v>1089</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>994</v>
+        <v>1090</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>995</v>
+        <v>1091</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>996</v>
+        <v>1092</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>998</v>
+        <v>1094</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>999</v>
+        <v>1095</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1000</v>
+        <v>1096</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1001</v>
+        <v>1097</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1002</v>
+        <v>1098</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1003</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -8837,4 +9481,56 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EEB36C5-BE5D-41BD-A3F1-97680DD72181}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA49DCDA-24E4-439E-AED7-8785D3C74108}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>